--- a/data/google-spreadsheet/M3GIM-Werkindex.xlsx
+++ b/data/google-spreadsheet/M3GIM-Werkindex.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="362">
   <si>
     <t>m3gim_id</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Beethoven, Ludwig van</t>
   </si>
   <si>
+    <t>9. Symphonie</t>
+  </si>
+  <si>
     <t>W3</t>
   </si>
   <si>
@@ -109,6 +112,15 @@
     <t>Auf dem grünen Balkon mein Mädchen schaut</t>
   </si>
   <si>
+    <t>W98</t>
+  </si>
+  <si>
+    <t>Ave Maria</t>
+  </si>
+  <si>
+    <t>Schubert, Franz</t>
+  </si>
+  <si>
     <t>W9</t>
   </si>
   <si>
@@ -178,6 +190,18 @@
     <t>Gaea</t>
   </si>
   <si>
+    <t>W127</t>
+  </si>
+  <si>
+    <t>Das Rheingold</t>
+  </si>
+  <si>
+    <t>Wagner, Richard</t>
+  </si>
+  <si>
+    <t>Fricka</t>
+  </si>
+  <si>
     <t>W17</t>
   </si>
   <si>
@@ -205,6 +229,12 @@
     <t>Octavian</t>
   </si>
   <si>
+    <t>Der Ring des Nibelungen</t>
+  </si>
+  <si>
+    <t>Fricka, Waltraute</t>
+  </si>
+  <si>
     <t>W20</t>
   </si>
   <si>
@@ -220,19 +250,46 @@
     <t>Die Geschöpfe des Prometheus</t>
   </si>
   <si>
+    <t>W125</t>
+  </si>
+  <si>
+    <t>die Götterdämmerung</t>
+  </si>
+  <si>
+    <t>Waltraute</t>
+  </si>
+  <si>
     <t>W22</t>
   </si>
   <si>
     <t>Die ihr schwebet um diese Palmen</t>
   </si>
   <si>
+    <t>W108</t>
+  </si>
+  <si>
+    <t>Die Jahreszeiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haydn, Joseph </t>
+  </si>
+  <si>
+    <t>Altsolo</t>
+  </si>
+  <si>
+    <t>W111</t>
+  </si>
+  <si>
+    <t>Die junge Magd</t>
+  </si>
+  <si>
     <t>W23</t>
   </si>
   <si>
     <t>Die Meistersinger von Nürnberg</t>
   </si>
   <si>
-    <t>Wagner, Richard</t>
+    <t>Q190891</t>
   </si>
   <si>
     <t>Magdalene</t>
@@ -241,201 +298,225 @@
     <t>Wagner, Richard (UAKUG/NIM_007_4)</t>
   </si>
   <si>
-    <t>W24</t>
-  </si>
-  <si>
-    <t>Q190891</t>
+    <t>W25</t>
+  </si>
+  <si>
+    <t>Die Walküre</t>
+  </si>
+  <si>
+    <t>Wagner, Richard (UAKUG/NIM_007_5_1)</t>
+  </si>
+  <si>
+    <t>W26</t>
+  </si>
+  <si>
+    <t>Die Zauberflöte</t>
+  </si>
+  <si>
+    <t>Zweite Dame</t>
+  </si>
+  <si>
+    <t>Mozart, Wolfgang (UAKUG/NIM_007_4)</t>
+  </si>
+  <si>
+    <t>W28</t>
+  </si>
+  <si>
+    <t>Don Giovanni</t>
+  </si>
+  <si>
+    <t>W96</t>
+  </si>
+  <si>
+    <t>E-Dur Messe</t>
+  </si>
+  <si>
+    <t>W29</t>
+  </si>
+  <si>
+    <t>Ein kleines Haus</t>
+  </si>
+  <si>
+    <t>W30</t>
+  </si>
+  <si>
+    <t>Elektra</t>
+  </si>
+  <si>
+    <t>Aufseherin</t>
+  </si>
+  <si>
+    <t>Strauss, Richard (UAKUG/NIM_007_4)</t>
+  </si>
+  <si>
+    <t>W115</t>
+  </si>
+  <si>
+    <t>Elias, op. 70, MWV A 25</t>
+  </si>
+  <si>
+    <t>Mendelssohn Bartholdy, Felix</t>
+  </si>
+  <si>
+    <t>W31</t>
+  </si>
+  <si>
+    <t>Er liebt mich nicht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schubert, Franz </t>
+  </si>
+  <si>
+    <t>W32</t>
+  </si>
+  <si>
+    <t>Es träumte mir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brahms, Johannes </t>
+  </si>
+  <si>
+    <t>W33</t>
+  </si>
+  <si>
+    <t>Evgenij Onegin</t>
+  </si>
+  <si>
+    <t>Čajkovskij, Pëtr Ilʹič</t>
+  </si>
+  <si>
+    <t>Olga und Filipjewna</t>
+  </si>
+  <si>
+    <t>W34</t>
+  </si>
+  <si>
+    <t>Falstaff</t>
+  </si>
+  <si>
+    <t>Quickly und Meg</t>
+  </si>
+  <si>
+    <t>W35</t>
+  </si>
+  <si>
+    <t>Führ mich, Kind, nach Bethlehem</t>
+  </si>
+  <si>
+    <t>W36</t>
+  </si>
+  <si>
+    <t>Ganymed</t>
+  </si>
+  <si>
+    <t>W37</t>
+  </si>
+  <si>
+    <t>Geh', Geliebter, geh' jetzt</t>
+  </si>
+  <si>
+    <t>W38</t>
+  </si>
+  <si>
+    <t>Gesang an die Hoffnung</t>
+  </si>
+  <si>
+    <t>W39</t>
+  </si>
+  <si>
+    <t>Glücks genug</t>
+  </si>
+  <si>
+    <t>W40</t>
+  </si>
+  <si>
+    <t>Götterdämmerung</t>
+  </si>
+  <si>
+    <t>Waltraute/Zweite Norn</t>
+  </si>
+  <si>
+    <t>W41</t>
+  </si>
+  <si>
+    <t>Herr, was trägt der Boden hier</t>
+  </si>
+  <si>
+    <t>W42</t>
+  </si>
+  <si>
+    <t>Herzog Blaubart's Burg</t>
+  </si>
+  <si>
+    <t>Bartók, Béla</t>
+  </si>
+  <si>
+    <t>Bartok, Bela  (UAKUG/NIM_007_2)</t>
+  </si>
+  <si>
+    <t>W43</t>
+  </si>
+  <si>
+    <t>Ich liebe dich</t>
+  </si>
+  <si>
+    <t>Beethoven, Ludwig von</t>
+  </si>
+  <si>
+    <t>W44</t>
+  </si>
+  <si>
+    <t>Il Trovatore</t>
+  </si>
+  <si>
+    <t>Azucena</t>
+  </si>
+  <si>
+    <t>W45</t>
+  </si>
+  <si>
+    <t>In dem Schatten meiner Locken</t>
+  </si>
+  <si>
+    <t>W100</t>
+  </si>
+  <si>
+    <t>Johannespassion</t>
+  </si>
+  <si>
+    <t>Bach, Johann Sebastian</t>
+  </si>
+  <si>
+    <t>W106</t>
+  </si>
+  <si>
+    <t>Judas Maccabaeus</t>
+  </si>
+  <si>
+    <t>Händel, Georg Friedrich</t>
+  </si>
+  <si>
+    <t>W46</t>
+  </si>
+  <si>
+    <t>Judith</t>
+  </si>
+  <si>
+    <t>Honegger, Arthur</t>
+  </si>
+  <si>
+    <t>W47</t>
+  </si>
+  <si>
+    <t>Julius Cäsar</t>
+  </si>
+  <si>
+    <t>Q729645</t>
   </si>
   <si>
     <t>Oper</t>
   </si>
   <si>
-    <t>W25</t>
-  </si>
-  <si>
-    <t>Die Walküre</t>
-  </si>
-  <si>
-    <t>Wagner, Richard (UAKUG/NIM_007_5_1)</t>
-  </si>
-  <si>
-    <t>W26</t>
-  </si>
-  <si>
-    <t>Die Zauberflöte</t>
-  </si>
-  <si>
-    <t>Zweite Dame</t>
-  </si>
-  <si>
-    <t>Mozart, Wolfgang (UAKUG/NIM_007_4)</t>
-  </si>
-  <si>
-    <t>W28</t>
-  </si>
-  <si>
-    <t>Don Giovanni</t>
-  </si>
-  <si>
-    <t>W29</t>
-  </si>
-  <si>
-    <t>Ein kleines Haus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haydn, Joseph </t>
-  </si>
-  <si>
-    <t>W30</t>
-  </si>
-  <si>
-    <t>Elektra</t>
-  </si>
-  <si>
-    <t>Aufseherin</t>
-  </si>
-  <si>
-    <t>Strauss, Richard (UAKUG/NIM_007_4)</t>
-  </si>
-  <si>
-    <t>W31</t>
-  </si>
-  <si>
-    <t>Er liebt mich nicht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schubert, Franz </t>
-  </si>
-  <si>
-    <t>W32</t>
-  </si>
-  <si>
-    <t>Es träumte mir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brahms, Johannes </t>
-  </si>
-  <si>
-    <t>W33</t>
-  </si>
-  <si>
-    <t>Evgenij Onegin</t>
-  </si>
-  <si>
-    <t>Čajkovskij, Pëtr Ilʹič</t>
-  </si>
-  <si>
-    <t>Olga und Filipjewna</t>
-  </si>
-  <si>
-    <t>W34</t>
-  </si>
-  <si>
-    <t>Falstaff</t>
-  </si>
-  <si>
-    <t>Quickly und Meg</t>
-  </si>
-  <si>
-    <t>W35</t>
-  </si>
-  <si>
-    <t>Führ mich, Kind, nach Bethlehem</t>
-  </si>
-  <si>
-    <t>W36</t>
-  </si>
-  <si>
-    <t>Ganymed</t>
-  </si>
-  <si>
-    <t>W37</t>
-  </si>
-  <si>
-    <t>Geh', Geliebter, geh' jetzt</t>
-  </si>
-  <si>
-    <t>W38</t>
-  </si>
-  <si>
-    <t>Gesang an die Hoffnung</t>
-  </si>
-  <si>
-    <t>W39</t>
-  </si>
-  <si>
-    <t>Glücks genug</t>
-  </si>
-  <si>
-    <t>W40</t>
-  </si>
-  <si>
-    <t>Götterdämmerung</t>
-  </si>
-  <si>
-    <t>Waltraute/Zweite Norn</t>
-  </si>
-  <si>
-    <t>W41</t>
-  </si>
-  <si>
-    <t>Herr, was trägt der Boden hier</t>
-  </si>
-  <si>
-    <t>W42</t>
-  </si>
-  <si>
-    <t>Herzog Blaubart's Burg</t>
-  </si>
-  <si>
-    <t>Bartok, Bela  (UAKUG/NIM_007_2)</t>
-  </si>
-  <si>
-    <t>W43</t>
-  </si>
-  <si>
-    <t>Ich liebe dich</t>
-  </si>
-  <si>
-    <t>Beethoven, Ludwig von</t>
-  </si>
-  <si>
-    <t>W44</t>
-  </si>
-  <si>
-    <t>Il Trovatore</t>
-  </si>
-  <si>
-    <t>Azucena</t>
-  </si>
-  <si>
-    <t>W45</t>
-  </si>
-  <si>
-    <t>In dem Schatten meiner Locken</t>
-  </si>
-  <si>
-    <t>W46</t>
-  </si>
-  <si>
-    <t>Judith</t>
-  </si>
-  <si>
-    <t>Honegger, Arthur</t>
-  </si>
-  <si>
-    <t>W47</t>
-  </si>
-  <si>
-    <t>Julius Cäsar</t>
-  </si>
-  <si>
-    <t>Q729645</t>
-  </si>
-  <si>
-    <t>Händel, Georg Friedrich</t>
-  </si>
-  <si>
     <t>W48</t>
   </si>
   <si>
@@ -448,6 +529,15 @@
     <t>Kabanicha</t>
   </si>
   <si>
+    <t>W114</t>
+  </si>
+  <si>
+    <t>Kindertotenlieder</t>
+  </si>
+  <si>
+    <t>Mahler, Gustav</t>
+  </si>
+  <si>
     <t>W49</t>
   </si>
   <si>
@@ -487,25 +577,64 @@
     <t>Le chant de la Terre</t>
   </si>
   <si>
-    <t>Mahler, Gustav</t>
-  </si>
-  <si>
     <t>Alt-Solo</t>
   </si>
   <si>
+    <t>W123</t>
+  </si>
+  <si>
+    <t>Le laudi di San Francesco d'Assisi</t>
+  </si>
+  <si>
+    <t>Suter, Hermann</t>
+  </si>
+  <si>
+    <t>W54</t>
+  </si>
+  <si>
+    <t>Le nozze di Figaro</t>
+  </si>
+  <si>
+    <t>W129</t>
+  </si>
+  <si>
+    <t>Les Noces</t>
+  </si>
+  <si>
+    <t>Stravinsky, Igor</t>
+  </si>
+  <si>
+    <t>W55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lied der Mignon </t>
+  </si>
+  <si>
     <t>Lied von der Erde</t>
   </si>
   <si>
-    <t>W54</t>
-  </si>
-  <si>
-    <t>Le nozze di Figaro</t>
-  </si>
-  <si>
-    <t>W55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lied der Mignon </t>
+    <t>W126</t>
+  </si>
+  <si>
+    <t>Lieder von der Erde</t>
+  </si>
+  <si>
+    <t>W117</t>
+  </si>
+  <si>
+    <t>Litaniae lauretanae  KV 109</t>
+  </si>
+  <si>
+    <t>W118</t>
+  </si>
+  <si>
+    <t>Litaniae lauretanae KV 195</t>
+  </si>
+  <si>
+    <t>W119</t>
+  </si>
+  <si>
+    <t>Requiem</t>
   </si>
   <si>
     <t>W56</t>
@@ -538,12 +667,66 @@
     <t>Suzuki</t>
   </si>
   <si>
+    <t>W112</t>
+  </si>
+  <si>
+    <t>Marienlieder</t>
+  </si>
+  <si>
+    <t>W101</t>
+  </si>
+  <si>
+    <t>Matthäuspassion</t>
+  </si>
+  <si>
     <t>W59</t>
   </si>
   <si>
     <t xml:space="preserve">Mein Herz ist stumm </t>
   </si>
   <si>
+    <t>W128</t>
+  </si>
+  <si>
+    <t>Meistersinger</t>
+  </si>
+  <si>
+    <t>W116</t>
+  </si>
+  <si>
+    <t>Messen, KV 317</t>
+  </si>
+  <si>
+    <t>W103</t>
+  </si>
+  <si>
+    <t>Messen, op. 123 (D-Dur)</t>
+  </si>
+  <si>
+    <t>Missa Solemnis</t>
+  </si>
+  <si>
+    <t>W105</t>
+  </si>
+  <si>
+    <t>Messen, WAB 28 (f-Moll)</t>
+  </si>
+  <si>
+    <t>Bruckner, Anton</t>
+  </si>
+  <si>
+    <t>W107</t>
+  </si>
+  <si>
+    <t>Messiah</t>
+  </si>
+  <si>
+    <t>W110</t>
+  </si>
+  <si>
+    <t>Missa in angustijs</t>
+  </si>
+  <si>
     <t>W60</t>
   </si>
   <si>
@@ -556,9 +739,6 @@
     <t>Nachtstück</t>
   </si>
   <si>
-    <t>Schubert, Franz</t>
-  </si>
-  <si>
     <t>W62</t>
   </si>
   <si>
@@ -634,6 +814,12 @@
     <t>keine Rollenangabe</t>
   </si>
   <si>
+    <t>W122</t>
+  </si>
+  <si>
+    <t>Pulcinella</t>
+  </si>
+  <si>
     <t>W70</t>
   </si>
   <si>
@@ -664,6 +850,24 @@
     <t>Regentropfen</t>
   </si>
   <si>
+    <t>W113</t>
+  </si>
+  <si>
+    <t>W124</t>
+  </si>
+  <si>
+    <t>W97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mozart, Wolfgang Amadeus </t>
+  </si>
+  <si>
+    <t>W104</t>
+  </si>
+  <si>
+    <t>Rhapsodien, Alt, Männerchor, Orchester, op. 53</t>
+  </si>
+  <si>
     <t>W74</t>
   </si>
   <si>
@@ -697,24 +901,36 @@
     <t>Strauss, Strauss (UAKUG/NIM_007_2)</t>
   </si>
   <si>
+    <t>W99</t>
+  </si>
+  <si>
+    <t>Sinfonien, Nr. 9, op. 125 (d-Moll)</t>
+  </si>
+  <si>
     <t>W78</t>
   </si>
   <si>
-    <t>Sinfonien, Nr. 9, op. 125 (d-Moll)</t>
-  </si>
-  <si>
     <t>W79</t>
   </si>
   <si>
     <t>Spanisches Liederbuch</t>
   </si>
   <si>
+    <t>W120</t>
+  </si>
+  <si>
+    <t>Stabat mater</t>
+  </si>
+  <si>
+    <t>Pergolesi, Giovanni Battista</t>
+  </si>
+  <si>
+    <t>W121</t>
+  </si>
+  <si>
     <t>W80</t>
   </si>
   <si>
-    <t>Stabat mater</t>
-  </si>
-  <si>
     <t>W81</t>
   </si>
   <si>
@@ -727,9 +943,6 @@
     <t>Svadebka</t>
   </si>
   <si>
-    <t>Stravinsky, Igor</t>
-  </si>
-  <si>
     <t>ohne Angabe</t>
   </si>
   <si>
@@ -754,6 +967,12 @@
     <t>Venus</t>
   </si>
   <si>
+    <t>W109</t>
+  </si>
+  <si>
+    <t>Theresienmesse</t>
+  </si>
+  <si>
     <t>W85</t>
   </si>
   <si>
@@ -799,6 +1018,12 @@
     <t>Von ewiger Liebe</t>
   </si>
   <si>
+    <t>W102</t>
+  </si>
+  <si>
+    <t>Weihnachts-Oratorium</t>
+  </si>
+  <si>
     <t>W91</t>
   </si>
   <si>
@@ -829,235 +1054,49 @@
     <t>Berg, Alban</t>
   </si>
   <si>
+    <t>W130</t>
+  </si>
+  <si>
+    <t>Sampiero Corso</t>
+  </si>
+  <si>
+    <t>Tomasi, Henri</t>
+  </si>
+  <si>
+    <t>W131</t>
+  </si>
+  <si>
+    <t>Siegfried</t>
+  </si>
+  <si>
+    <t>W132</t>
+  </si>
+  <si>
+    <t>Die Favoritin</t>
+  </si>
+  <si>
+    <t>Donizetti, Gaetano</t>
+  </si>
+  <si>
+    <t>W133</t>
+  </si>
+  <si>
+    <t>Die schwarze Spinne</t>
+  </si>
+  <si>
+    <t>W134</t>
+  </si>
+  <si>
+    <t>W135</t>
+  </si>
+  <si>
+    <t>W136</t>
+  </si>
+  <si>
+    <t>W137</t>
+  </si>
+  <si>
     <t>W95</t>
-  </si>
-  <si>
-    <t>W96</t>
-  </si>
-  <si>
-    <t>E-Dur Messe</t>
-  </si>
-  <si>
-    <t>W97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requium </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mozart, Wolfgang Amadeus </t>
-  </si>
-  <si>
-    <t>W98</t>
-  </si>
-  <si>
-    <t>Ave Maria</t>
-  </si>
-  <si>
-    <t>W99</t>
-  </si>
-  <si>
-    <t>Altsolo</t>
-  </si>
-  <si>
-    <t>W100</t>
-  </si>
-  <si>
-    <t>Johannespassion</t>
-  </si>
-  <si>
-    <t>Bach, Johann Sebastian</t>
-  </si>
-  <si>
-    <t>W101</t>
-  </si>
-  <si>
-    <t>Matthäuspassion</t>
-  </si>
-  <si>
-    <t>W102</t>
-  </si>
-  <si>
-    <t>Weihnachts-Oratorium</t>
-  </si>
-  <si>
-    <t>W103</t>
-  </si>
-  <si>
-    <t>Messen, op. 123 (D-Dur)</t>
-  </si>
-  <si>
-    <t>Missa Solemnis</t>
-  </si>
-  <si>
-    <t>W104</t>
-  </si>
-  <si>
-    <t>Rhapsodien, Alt, Männerchor, Orchester, op. 53</t>
-  </si>
-  <si>
-    <t>W105</t>
-  </si>
-  <si>
-    <t>Messen, WAB 28 (f-Moll)</t>
-  </si>
-  <si>
-    <t>Bruckner, Anton</t>
-  </si>
-  <si>
-    <t>W106</t>
-  </si>
-  <si>
-    <t>Judas Maccabaeus</t>
-  </si>
-  <si>
-    <t>W107</t>
-  </si>
-  <si>
-    <t>Messiah</t>
-  </si>
-  <si>
-    <t>W108</t>
-  </si>
-  <si>
-    <t>Die Jahreszeiten</t>
-  </si>
-  <si>
-    <t>W109</t>
-  </si>
-  <si>
-    <t>Theresienmesse</t>
-  </si>
-  <si>
-    <t>W110</t>
-  </si>
-  <si>
-    <t>Missa in angustijs</t>
-  </si>
-  <si>
-    <t>W111</t>
-  </si>
-  <si>
-    <t>Die junge Magd</t>
-  </si>
-  <si>
-    <t>W112</t>
-  </si>
-  <si>
-    <t>Marienlieder</t>
-  </si>
-  <si>
-    <t>W113</t>
-  </si>
-  <si>
-    <t>Requiem</t>
-  </si>
-  <si>
-    <t>W114</t>
-  </si>
-  <si>
-    <t>Kindertotenlieder</t>
-  </si>
-  <si>
-    <t>W115</t>
-  </si>
-  <si>
-    <t>Elias, op. 70, MWV A 25</t>
-  </si>
-  <si>
-    <t>Mendelssohn Bartholdy, Felix</t>
-  </si>
-  <si>
-    <t>W116</t>
-  </si>
-  <si>
-    <t>Messen, KV 317</t>
-  </si>
-  <si>
-    <t>W117</t>
-  </si>
-  <si>
-    <t>Litaniae lauretanae  KV 109</t>
-  </si>
-  <si>
-    <t>W118</t>
-  </si>
-  <si>
-    <t>Litaniae lauretanae KV 195</t>
-  </si>
-  <si>
-    <t>W119</t>
-  </si>
-  <si>
-    <t>W120</t>
-  </si>
-  <si>
-    <t>Pergolesi, Giovanni Battista</t>
-  </si>
-  <si>
-    <t>W121</t>
-  </si>
-  <si>
-    <t>W122</t>
-  </si>
-  <si>
-    <t>Pulcinella</t>
-  </si>
-  <si>
-    <t>W123</t>
-  </si>
-  <si>
-    <t>Le laudi di San Francesco d'Assisi</t>
-  </si>
-  <si>
-    <t>Suter, Hermann</t>
-  </si>
-  <si>
-    <t>W124</t>
-  </si>
-  <si>
-    <t>W125</t>
-  </si>
-  <si>
-    <t>die Götterdämmerung</t>
-  </si>
-  <si>
-    <t>Waltraute</t>
-  </si>
-  <si>
-    <t>W126</t>
-  </si>
-  <si>
-    <t>W127</t>
-  </si>
-  <si>
-    <t>W128</t>
-  </si>
-  <si>
-    <t>W129</t>
-  </si>
-  <si>
-    <t>W130</t>
-  </si>
-  <si>
-    <t>W131</t>
-  </si>
-  <si>
-    <t>W132</t>
-  </si>
-  <si>
-    <t>W133</t>
-  </si>
-  <si>
-    <t>W134</t>
-  </si>
-  <si>
-    <t>W135</t>
-  </si>
-  <si>
-    <t>W136</t>
-  </si>
-  <si>
-    <t>W137</t>
   </si>
 </sst>
 </file>
@@ -1182,14 +1221,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1211,15 +1250,21 @@
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1231,7 +1276,7 @@
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1503,142 +1548,140 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>43</v>
@@ -1646,93 +1689,93 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>51</v>
+      <c r="E16" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="E20" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1744,237 +1787,240 @@
         <v>68</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="7" t="s">
         <v>70</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="3"/>
+      <c r="B24" s="7" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>97</v>
+        <v>61</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>100</v>
+        <v>61</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>25</v>
+      <c r="E38" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="40">
@@ -1985,63 +2031,60 @@
         <v>119</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="10" t="s">
         <v>122</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="4" t="s">
         <v>125</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>128</v>
+        <v>15</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="7" t="s">
         <v>130</v>
       </c>
+      <c r="B44" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="D44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45">
@@ -2052,166 +2095,175 @@
         <v>133</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>135</v>
+      <c r="D46" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9" t="s">
-        <v>78</v>
+      <c r="D47" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>143</v>
+        <v>61</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>147</v>
+        <v>15</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>150</v>
+        <v>143</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>152</v>
+        <v>147</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="D53" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>159</v>
+        <v>15</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="D54" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>128</v>
+      <c r="E56" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="C57" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E57" s="4" t="s">
+      <c r="D57" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2219,28 +2271,28 @@
       <c r="A58" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="10" t="s">
         <v>169</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B59" s="7" t="s">
         <v>172</v>
       </c>
+      <c r="B59" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="D59" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -2251,89 +2303,82 @@
         <v>176</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>28</v>
+        <v>54</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B61" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>15</v>
+      <c r="B61" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>186</v>
+        <v>174</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9" t="s">
         <v>189</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="B66" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9" t="s">
-        <v>78</v>
+      <c r="D66" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
@@ -2344,751 +2389,758 @@
         <v>195</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E67" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>201</v>
+      <c r="D68" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>73</v>
+        <v>174</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>209</v>
+        <v>54</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>212</v>
+        <v>54</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>97</v>
+        <v>207</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9" t="s">
-        <v>189</v>
+        <v>208</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>218</v>
+        <v>211</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>25</v>
+        <v>214</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>223</v>
+        <v>218</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>219</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="D78" s="4"/>
+        <v>220</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="E78" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>227</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>229</v>
+        <v>222</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>14</v>
+        <v>225</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>235</v>
+        <v>228</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>229</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>90</v>
+        <v>11</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>237</v>
+        <v>231</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>232</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>239</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>241</v>
+        <v>234</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>243</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>245</v>
+        <v>236</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>237</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>246</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>186</v>
+        <v>15</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>253</v>
+        <v>242</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>254</v>
+        <v>15</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>259</v>
+        <v>247</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>8</v>
+        <v>250</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>22</v>
+        <v>253</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F92" s="16" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>266</v>
+        <v>259</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9" t="s">
-        <v>189</v>
+        <v>262</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>270</v>
+        <v>264</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>265</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>271</v>
+        <v>123</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>170</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B100" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="4" t="s">
+      <c r="B101" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B100" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="D100" s="4" t="s">
+      <c r="B102" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E100" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="3" t="s">
+      <c r="E109" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B110" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="4" t="s">
+      <c r="D110" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B111" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D108" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="3" t="s">
+      <c r="D111" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B112" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="4" t="s">
+      <c r="D112" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="E112" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="3" t="s">
+      <c r="B113" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B114" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="4" t="s">
+      <c r="B115" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="D115" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="3" t="s">
+      <c r="B116" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="D116" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D113" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="4" t="s">
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B117" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="3" t="s">
+      <c r="D117" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="E117" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D115" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="4" t="s">
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B118" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D118" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E118" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="3" t="s">
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B119" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D117" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="4" t="s">
+      <c r="D119" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B120" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D118" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="3" t="s">
+      <c r="D120" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B121" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D119" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="4" t="s">
+      <c r="D121" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E121" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="3" t="s">
+      <c r="F121" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="B122" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="4" t="s">
+      <c r="D122" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B122" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>281</v>
-      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="4" t="s">
         <v>328</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>329</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>281</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B124" s="4" t="s">
@@ -3097,99 +3149,151 @@
       <c r="D124" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E124" s="4" t="s">
-        <v>281</v>
-      </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="4" t="s">
         <v>333</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>281</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="4" t="s">
-        <v>334</v>
+      <c r="A126" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>336</v>
+        <v>87</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="4" t="s">
         <v>337</v>
       </c>
+      <c r="B127" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="4" t="s">
-        <v>338</v>
+      <c r="A128" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="3" t="s">
-        <v>339</v>
+      <c r="A129" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B129" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C129" s="13"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="13" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="4" t="s">
-        <v>340</v>
+      <c r="A130" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="3" t="s">
-        <v>341</v>
+      <c r="A131" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="4" t="s">
-        <v>342</v>
+      <c r="A132" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="3" t="s">
-        <v>343</v>
+      <c r="A133" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="4" t="s">
-        <v>344</v>
+      <c r="A134" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="3" t="s">
-        <v>345</v>
+      <c r="A135" s="4" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="4" t="s">
-        <v>346</v>
+      <c r="A136" s="3" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="3" t="s">
-        <v>347</v>
+      <c r="A137" s="4" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="139" ht="15.75" customHeight="1"/>
+      <c r="A138" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
     <row r="140" ht="15.75" customHeight="1"/>
     <row r="141" ht="15.75" customHeight="1"/>
     <row r="142" ht="15.75" customHeight="1"/>
@@ -3315,49 +3419,49 @@
     <row r="262" ht="15.75" customHeight="1"/>
     <row r="263" ht="15.75" customHeight="1"/>
     <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1">
-      <c r="B265" s="17"/>
-      <c r="C265" s="17"/>
-      <c r="D265" s="17"/>
-      <c r="E265" s="17"/>
-      <c r="F265" s="17"/>
-    </row>
+    <row r="265" ht="15.75" customHeight="1"/>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="B266" s="17"/>
-      <c r="C266" s="17"/>
-      <c r="D266" s="17"/>
-      <c r="E266" s="17"/>
-      <c r="F266" s="17"/>
+      <c r="B266" s="19"/>
+      <c r="C266" s="19"/>
+      <c r="D266" s="19"/>
+      <c r="E266" s="19"/>
+      <c r="F266" s="19"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="B267" s="17"/>
-      <c r="C267" s="17"/>
-      <c r="D267" s="17"/>
-      <c r="E267" s="17"/>
-      <c r="F267" s="17"/>
+      <c r="B267" s="19"/>
+      <c r="C267" s="19"/>
+      <c r="D267" s="19"/>
+      <c r="E267" s="19"/>
+      <c r="F267" s="19"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="B268" s="17"/>
-      <c r="C268" s="17"/>
-      <c r="D268" s="17"/>
-      <c r="E268" s="17"/>
-      <c r="F268" s="17"/>
+      <c r="B268" s="19"/>
+      <c r="C268" s="19"/>
+      <c r="D268" s="19"/>
+      <c r="E268" s="19"/>
+      <c r="F268" s="19"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="B269" s="17"/>
-      <c r="C269" s="17"/>
-      <c r="D269" s="17"/>
-      <c r="E269" s="17"/>
-      <c r="F269" s="17"/>
+      <c r="B269" s="19"/>
+      <c r="C269" s="19"/>
+      <c r="D269" s="19"/>
+      <c r="E269" s="19"/>
+      <c r="F269" s="19"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="B270" s="17"/>
-      <c r="C270" s="17"/>
-      <c r="D270" s="17"/>
-      <c r="E270" s="17"/>
-      <c r="F270" s="17"/>
-    </row>
-    <row r="271" ht="15.75" customHeight="1"/>
+      <c r="B270" s="19"/>
+      <c r="C270" s="19"/>
+      <c r="D270" s="19"/>
+      <c r="E270" s="19"/>
+      <c r="F270" s="19"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="B271" s="19"/>
+      <c r="C271" s="19"/>
+      <c r="D271" s="19"/>
+      <c r="E271" s="19"/>
+      <c r="F271" s="19"/>
+    </row>
     <row r="272" ht="15.75" customHeight="1"/>
     <row r="273" ht="15.75" customHeight="1"/>
     <row r="274" ht="15.75" customHeight="1"/>
@@ -4131,6 +4235,7 @@
     <row r="1042" ht="15.75" customHeight="1"/>
     <row r="1043" ht="15.75" customHeight="1"/>
     <row r="1044" ht="15.75" customHeight="1"/>
+    <row r="1045" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
